--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.91491</v>
+        <v>17.43145</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0754</v>
+        <v>16.93627</v>
       </c>
       <c r="E2" t="n">
-        <v>16.89005</v>
+        <v>16.95824</v>
       </c>
       <c r="F2" t="n">
-        <v>42.83607</v>
+        <v>44.09531</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05057</v>
+        <v>0.05154</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8435</v>
+        <v>1.89741</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.57276</v>
+        <v>17.31105</v>
       </c>
       <c r="D3" t="n">
-        <v>17.02332</v>
+        <v>17.10083</v>
       </c>
       <c r="E3" t="n">
-        <v>16.80957</v>
+        <v>17.10667</v>
       </c>
       <c r="F3" t="n">
-        <v>43.69275</v>
+        <v>42.59602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05179</v>
+        <v>0.05207</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83657</v>
+        <v>1.8749</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.90887</v>
+        <v>17.22546</v>
       </c>
       <c r="D4" t="n">
-        <v>17.39873</v>
+        <v>16.81535</v>
       </c>
       <c r="E4" t="n">
-        <v>16.94171</v>
+        <v>17.13835</v>
       </c>
       <c r="F4" t="n">
-        <v>43.93268</v>
+        <v>43.92479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05142</v>
+        <v>0.05124</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84548</v>
+        <v>1.81672</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.15139</v>
+        <v>16.72811</v>
       </c>
       <c r="D6" t="n">
-        <v>16.52729</v>
+        <v>16.13981</v>
       </c>
       <c r="E6" t="n">
-        <v>16.20925</v>
+        <v>16.70357</v>
       </c>
       <c r="F6" t="n">
-        <v>21.88561</v>
+        <v>22.06683</v>
       </c>
       <c r="G6" t="n">
-        <v>34.76359</v>
+        <v>35.09506</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.22018</v>
+        <v>17.20763</v>
       </c>
       <c r="D7" t="n">
-        <v>16.78139</v>
+        <v>16.23397</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56212</v>
+        <v>16.84625</v>
       </c>
       <c r="F7" t="n">
-        <v>22.15983</v>
+        <v>21.79852</v>
       </c>
       <c r="G7" t="n">
-        <v>34.52999</v>
+        <v>34.72253</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.75872</v>
+        <v>16.96437</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20201</v>
+        <v>16.2885</v>
       </c>
       <c r="E8" t="n">
-        <v>16.95539</v>
+        <v>16.55058</v>
       </c>
       <c r="F8" t="n">
-        <v>21.99382</v>
+        <v>22.11599</v>
       </c>
       <c r="G8" t="n">
-        <v>34.3648</v>
+        <v>35.05556</v>
       </c>
     </row>
   </sheetData>
